--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.04477375603241</v>
+        <v>1.794775735355267</v>
       </c>
       <c r="D2" t="n">
-        <v>10.85266921677905</v>
+        <v>1.763558747726596</v>
       </c>
       <c r="E2" t="n">
-        <v>7.596115462501935</v>
+        <v>1.234368762656564</v>
       </c>
       <c r="F2" t="n">
-        <v>7.585469231675791</v>
+        <v>1.232638750147316</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.84790020892513</v>
+        <v>4.687783783950333</v>
       </c>
       <c r="D3" t="n">
-        <v>28.91715133242678</v>
+        <v>4.699037091519353</v>
       </c>
       <c r="E3" t="n">
-        <v>7.596115462501935</v>
+        <v>1.234368762656564</v>
       </c>
       <c r="F3" t="n">
-        <v>7.585469231675791</v>
+        <v>1.232638750147316</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.38524813113355</v>
+        <v>2.987602821309201</v>
       </c>
       <c r="D4" t="n">
-        <v>18.54871309796962</v>
+        <v>3.014165878420064</v>
       </c>
       <c r="E4" t="n">
-        <v>7.596115462501935</v>
+        <v>1.234368762656564</v>
       </c>
       <c r="F4" t="n">
-        <v>7.585469231675791</v>
+        <v>1.232638750147316</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.44513452225801</v>
+        <v>4.622334359866927</v>
       </c>
       <c r="D5" t="n">
-        <v>28.55693471837509</v>
+        <v>4.640501891735952</v>
       </c>
       <c r="E5" t="n">
-        <v>7.596115462501935</v>
+        <v>1.234368762656564</v>
       </c>
       <c r="F5" t="n">
-        <v>7.585469231675791</v>
+        <v>1.232638750147316</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.85924355526294</v>
+        <v>5.014627077730228</v>
       </c>
       <c r="D6" t="n">
-        <v>30.45085711695755</v>
+        <v>4.948264281505603</v>
       </c>
       <c r="E6" t="n">
-        <v>7.596115462501935</v>
+        <v>1.234368762656564</v>
       </c>
       <c r="F6" t="n">
-        <v>7.585469231675791</v>
+        <v>1.232638750147316</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
